--- a/excel_exports/DTI.xlsx
+++ b/excel_exports/DTI.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="6" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="7" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1275,4 +1277,1648 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Roll No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Manually Edited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Student 14</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Student 19</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Student 20</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Student 21</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Student 22</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Student 24</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Student 26</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Student 27</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Student 28</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Student 29</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Student 30</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Student 31</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Student 32</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Student 33</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Student 34</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Student 36</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Student 37</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Student 38</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Student 44</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Student 45</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Student 46</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Student 48</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Student 49</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Student 50</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>07:35:25</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Roll No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Manually Edited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Student 14</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Student 19</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Student 20</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Student 21</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Student 22</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Student 24</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Student 26</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Student 27</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Student 28</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Student 29</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Student 30</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Student 31</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Student 32</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Student 33</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Student 34</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Student 36</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Student 37</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Student 38</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Student 44</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Student 45</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Student 46</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Student 48</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Student 49</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Student 50</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>07:38:05</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>